--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.30339308744594</v>
+        <v>4.274301376709966</v>
       </c>
       <c r="D2" t="n">
-        <v>2.107881886095655</v>
+        <v>0.3425308064905438</v>
       </c>
       <c r="E2" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F2" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.40654279935374</v>
+        <v>2.178563204894982</v>
       </c>
       <c r="D3" t="n">
-        <v>14.11256840483866</v>
+        <v>2.293292365786282</v>
       </c>
       <c r="E3" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F3" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.82723123231108</v>
+        <v>8.74692507525055</v>
       </c>
       <c r="D4" t="n">
-        <v>48.43487127875246</v>
+        <v>7.870666582797275</v>
       </c>
       <c r="E4" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F4" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.87174330655886</v>
+        <v>5.341658287315815</v>
       </c>
       <c r="D5" t="n">
-        <v>32.7664012390395</v>
+        <v>5.324540201343918</v>
       </c>
       <c r="E5" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F5" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.53872564397553</v>
+        <v>7.237542917146024</v>
       </c>
       <c r="D6" t="n">
-        <v>44.46646702822919</v>
+        <v>7.225800892087244</v>
       </c>
       <c r="E6" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F6" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>75.7725915459807</v>
+        <v>12.31304612622186</v>
       </c>
       <c r="D7" t="n">
-        <v>75.71483005631615</v>
+        <v>12.30365988415137</v>
       </c>
       <c r="E7" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F7" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.91359725737535</v>
+        <v>6.323459554323494</v>
       </c>
       <c r="D8" t="n">
-        <v>35.75116064589155</v>
+        <v>5.809563604957376</v>
       </c>
       <c r="E8" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F8" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.78535874676567</v>
+        <v>6.627620796349422</v>
       </c>
       <c r="D9" t="n">
-        <v>33.59241419533401</v>
+        <v>5.458767306741777</v>
       </c>
       <c r="E9" t="n">
-        <v>17.44182483899382</v>
+        <v>2.834296536336496</v>
       </c>
       <c r="F9" t="n">
-        <v>20.75899199650362</v>
+        <v>3.373336199431838</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
